--- a/AAII_Financials/Yearly/FMFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FMFG_YR_FIN.xlsx
@@ -2174,7 +2174,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>67500</v>
+        <v>55000</v>
       </c>
       <c r="E58" s="3">
         <v>10600</v>
@@ -2240,7 +2240,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>789300</v>
+        <v>776800</v>
       </c>
       <c r="E60" s="3">
         <v>770400</v>
@@ -2273,7 +2273,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13000</v>
+        <v>25500</v>
       </c>
       <c r="E61" s="3">
         <v>12800</v>
